--- a/output/balance_sheet_templates/us_biodiesel_bal_sheets.xlsx
+++ b/output/balance_sheet_templates/us_biodiesel_bal_sheets.xlsx
@@ -3643,46 +3643,46 @@
         <v>1.14</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>0.455571447905</v>
+        <v>0.42269515785</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>6.412089965169</v>
+        <v>7.433347262355</v>
       </c>
       <c r="P42" s="13" t="n">
-        <v>19.0695630117895</v>
+        <v>18.9613383799175</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>7.297786228572</v>
+        <v>6.89104478048</v>
       </c>
       <c r="R42" s="13" t="n">
-        <v>3.459062904738</v>
+        <v>3.21090358176</v>
       </c>
       <c r="S42" s="13" t="n">
-        <v>7.24240932555</v>
+        <v>8.277517107334999</v>
       </c>
       <c r="T42" s="13" t="n">
-        <v>8.955845089169999</v>
+        <v>9.571556071105</v>
       </c>
       <c r="U42" s="13" t="n">
-        <v>8.463195082685001</v>
+        <v>9.310670601469999</v>
       </c>
       <c r="V42" s="13" t="n">
-        <v>4.8949757516625</v>
+        <v>7.41925190041</v>
       </c>
       <c r="W42" s="13" t="n">
-        <v>12.10734626073</v>
+        <v>15.58240630772</v>
       </c>
       <c r="X42" s="13" t="n">
-        <v>21.71994841205</v>
+        <v>30.63070937808</v>
       </c>
       <c r="Y42" s="13" t="n">
-        <v>30.188792352705</v>
+        <v>38.7374560174175</v>
       </c>
       <c r="Z42" s="13" t="n">
-        <v>1.534436185135</v>
+        <v>2.3480369539725</v>
       </c>
       <c r="AA42" s="13" t="n">
-        <v>0.2385120019275</v>
+        <v>0.82764731686</v>
       </c>
       <c r="AB42" s="13" t="n">
         <v>14.19</v>
@@ -3738,46 +3738,46 @@
         <v>1.71</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1.8139240481915</v>
+        <v>1.683022312755</v>
       </c>
       <c r="O43" s="14" t="n">
-        <v>6.158388792731</v>
+        <v>5.9243759323175</v>
       </c>
       <c r="P43" s="14" t="n">
-        <v>15.868143695467</v>
+        <v>15.66703766502</v>
       </c>
       <c r="Q43" s="14" t="n">
-        <v>7.4709201633185</v>
+        <v>7.2817138340625</v>
       </c>
       <c r="R43" s="14" t="n">
-        <v>19.373158848582</v>
+        <v>19.05274143129</v>
       </c>
       <c r="S43" s="14" t="n">
-        <v>7.6239535882125</v>
+        <v>8.478095950729999</v>
       </c>
       <c r="T43" s="14" t="n">
-        <v>7.476355340335</v>
+        <v>7.65167180456</v>
       </c>
       <c r="U43" s="14" t="n">
-        <v>11.457197450405</v>
+        <v>12.311662804735</v>
       </c>
       <c r="V43" s="14" t="n">
-        <v>5.6428271039</v>
+        <v>8.18047517238</v>
       </c>
       <c r="W43" s="14" t="n">
-        <v>2.5391885511125</v>
+        <v>4.140804257275</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>20.0104702378175</v>
+        <v>28.39026318023</v>
       </c>
       <c r="Y43" s="14" t="n">
-        <v>32.0551987476525</v>
+        <v>41.4961056558825</v>
       </c>
       <c r="Z43" s="14" t="n">
-        <v>1.42546444929</v>
+        <v>5.04983477271</v>
       </c>
       <c r="AA43" s="14" t="n">
-        <v>0.0440968348625</v>
+        <v>0.095658933265</v>
       </c>
       <c r="AB43" s="14" t="n">
         <v>15</v>
@@ -3833,46 +3833,46 @@
         <v>0.6</v>
       </c>
       <c r="N44" s="13" t="n">
-        <v>13.63680851267</v>
+        <v>14.375434834215</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>8.271192457710001</v>
+        <v>7.6743269127</v>
       </c>
       <c r="P44" s="13" t="n">
-        <v>12.801658826194</v>
+        <v>12.535215525805</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>21.7340633502825</v>
+        <v>21.7198255792175</v>
       </c>
       <c r="R44" s="13" t="n">
-        <v>26.5521911325265</v>
+        <v>26.297493817595</v>
       </c>
       <c r="S44" s="13" t="n">
-        <v>9.7984351649975</v>
+        <v>11.203900716015</v>
       </c>
       <c r="T44" s="13" t="n">
-        <v>16.8698112713725</v>
+        <v>17.8409952060725</v>
       </c>
       <c r="U44" s="13" t="n">
-        <v>9.54440639936</v>
+        <v>10.9084284862</v>
       </c>
       <c r="V44" s="13" t="n">
-        <v>7.536564418495</v>
+        <v>10.96690668192</v>
       </c>
       <c r="W44" s="13" t="n">
-        <v>19.91983931014</v>
+        <v>24.218003197885</v>
       </c>
       <c r="X44" s="13" t="n">
-        <v>24.08491491462</v>
+        <v>33.8756499156775</v>
       </c>
       <c r="Y44" s="13" t="n">
-        <v>19.9972083809925</v>
+        <v>26.57138914836</v>
       </c>
       <c r="Z44" s="13" t="n">
-        <v>0.964162123925</v>
+        <v>3.445481546045</v>
       </c>
       <c r="AA44" s="13" t="n">
-        <v>0.0477337290675</v>
+        <v>0.126262927665</v>
       </c>
       <c r="AB44" s="13" t="n">
         <v>12.89</v>
@@ -3928,43 +3928,43 @@
         <v>0.76</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>10.39877996532025</v>
+        <v>11.21676407292</v>
       </c>
       <c r="O45" s="14" t="n">
-        <v>5.3673183428515</v>
+        <v>5.06253442023</v>
       </c>
       <c r="P45" s="14" t="n">
-        <v>11.093631680103</v>
+        <v>10.935163325765</v>
       </c>
       <c r="Q45" s="14" t="n">
-        <v>37.4618950213445</v>
+        <v>36.86155615471</v>
       </c>
       <c r="R45" s="14" t="n">
-        <v>23.788563149862</v>
+        <v>23.4083896210325</v>
       </c>
       <c r="S45" s="14" t="n">
-        <v>9.002879401845</v>
+        <v>9.66386989806</v>
       </c>
       <c r="T45" s="14" t="n">
-        <v>12.2647280621075</v>
+        <v>14.21481108901</v>
       </c>
       <c r="U45" s="14" t="n">
-        <v>16.88501532844</v>
+        <v>19.316997504945</v>
       </c>
       <c r="V45" s="14" t="n">
-        <v>11.540223824535</v>
+        <v>15.880805464545</v>
       </c>
       <c r="W45" s="14" t="n">
-        <v>12.9707528448925</v>
+        <v>16.95473042907</v>
       </c>
       <c r="X45" s="14" t="n">
-        <v>23.038218723135</v>
+        <v>30.92726599802</v>
       </c>
       <c r="Y45" s="14" t="n">
-        <v>38.50225996995</v>
+        <v>47.612793785655</v>
       </c>
       <c r="Z45" s="14" t="n">
-        <v>0.287390713925</v>
+        <v>1.00667678916</v>
       </c>
       <c r="AA45" s="14" t="n">
         <v>17.59</v>
@@ -4023,43 +4023,43 @@
         <v>1.79</v>
       </c>
       <c r="N46" s="13" t="n">
-        <v>16.331430473498</v>
+        <v>16.175919066405</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>3.8380064665985</v>
+        <v>3.561043542945</v>
       </c>
       <c r="P46" s="13" t="n">
-        <v>10.696091016702</v>
+        <v>10.964171640905</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>40.754767315157</v>
+        <v>40.2481827094725</v>
       </c>
       <c r="R46" s="13" t="n">
-        <v>32.735336220937</v>
+        <v>32.28620746673</v>
       </c>
       <c r="S46" s="13" t="n">
-        <v>9.6131481088825</v>
+        <v>10.09595388102</v>
       </c>
       <c r="T46" s="13" t="n">
-        <v>8.825232998960001</v>
+        <v>9.811552530535</v>
       </c>
       <c r="U46" s="13" t="n">
-        <v>13.803987035545</v>
+        <v>15.07840395229</v>
       </c>
       <c r="V46" s="13" t="n">
-        <v>6.8609912360675</v>
+        <v>9.916697707559999</v>
       </c>
       <c r="W46" s="13" t="n">
-        <v>7.9699272744525</v>
+        <v>10.027007999435</v>
       </c>
       <c r="X46" s="13" t="n">
-        <v>18.9763674702</v>
+        <v>27.38284312876</v>
       </c>
       <c r="Y46" s="13" t="n">
-        <v>22.7246444549075</v>
+        <v>28.9494181185825</v>
       </c>
       <c r="Z46" s="13" t="n">
-        <v>0.145128354</v>
+        <v>0.48107472189</v>
       </c>
       <c r="AA46" s="13" t="n">
         <v>11.46</v>
@@ -4118,43 +4118,43 @@
         <v>3.14</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>21.82059201405125</v>
+        <v>22.833162716945</v>
       </c>
       <c r="O47" s="14" t="n">
-        <v>6.7545454720555</v>
+        <v>6.5303054707625</v>
       </c>
       <c r="P47" s="14" t="n">
-        <v>23.125874414958</v>
+        <v>22.81182991234</v>
       </c>
       <c r="Q47" s="14" t="n">
-        <v>52.754175983635</v>
+        <v>52.15750537977</v>
       </c>
       <c r="R47" s="14" t="n">
-        <v>60.185288362227</v>
+        <v>59.8845050206725</v>
       </c>
       <c r="S47" s="14" t="n">
-        <v>8.328664057507501</v>
+        <v>8.9407043467</v>
       </c>
       <c r="T47" s="14" t="n">
-        <v>9.189086511867499</v>
+        <v>9.7626987451</v>
       </c>
       <c r="U47" s="14" t="n">
-        <v>12.8146876935175</v>
+        <v>13.92652655408</v>
       </c>
       <c r="V47" s="14" t="n">
-        <v>10.7300157967625</v>
+        <v>14.508396801325</v>
       </c>
       <c r="W47" s="14" t="n">
-        <v>8.784863772930001</v>
+        <v>11.518630247075</v>
       </c>
       <c r="X47" s="14" t="n">
-        <v>20.821488321305</v>
+        <v>32.013808367835</v>
       </c>
       <c r="Y47" s="14" t="n">
-        <v>16.2264125049425</v>
+        <v>22.976505457675</v>
       </c>
       <c r="Z47" s="14" t="n">
-        <v>0.1372489001625</v>
+        <v>0.47637925734</v>
       </c>
       <c r="AA47" s="14" t="n">
         <v>12.3</v>
@@ -4213,43 +4213,43 @@
         <v>3.95</v>
       </c>
       <c r="N48" s="13" t="n">
-        <v>11.0817052465</v>
+        <v>11.34046073027</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>16.936027089128</v>
+        <v>16.5405547714575</v>
       </c>
       <c r="P48" s="13" t="n">
-        <v>40.0685906425875</v>
+        <v>39.2844021331475</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>57.709305713752</v>
+        <v>57.1774525975275</v>
       </c>
       <c r="R48" s="13" t="n">
-        <v>58.0247981640775</v>
+        <v>57.60116282144</v>
       </c>
       <c r="S48" s="13" t="n">
-        <v>4.34185703721</v>
+        <v>4.595013570315</v>
       </c>
       <c r="T48" s="13" t="n">
-        <v>11.0232104378375</v>
+        <v>12.24328620445</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>10.93055321127</v>
+        <v>11.427975732285</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>7.1129350853225</v>
+        <v>10.15120562764</v>
       </c>
       <c r="W48" s="13" t="n">
-        <v>5.170271851395</v>
+        <v>7.554056290025</v>
       </c>
       <c r="X48" s="13" t="n">
-        <v>15.063741304675</v>
+        <v>24.096587675055</v>
       </c>
       <c r="Y48" s="13" t="n">
-        <v>12.9072092797025</v>
+        <v>19.9176110981925</v>
       </c>
       <c r="Z48" s="13" t="n">
-        <v>0.0165559331</v>
+        <v>0.0157586142</v>
       </c>
       <c r="AA48" s="13" t="n">
         <v>9.56</v>
@@ -4308,43 +4308,43 @@
         <v>1.31</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>15.97052963912875</v>
+        <v>16.605963873695</v>
       </c>
       <c r="O49" s="14" t="n">
-        <v>19.6976830383865</v>
+        <v>19.157508862345</v>
       </c>
       <c r="P49" s="14" t="n">
-        <v>30.8207519896325</v>
+        <v>30.51693763587</v>
       </c>
       <c r="Q49" s="14" t="n">
-        <v>62.7649894517905</v>
+        <v>62.0937905456925</v>
       </c>
       <c r="R49" s="14" t="n">
-        <v>53.47911220813</v>
+        <v>52.8007688519675</v>
       </c>
       <c r="S49" s="14" t="n">
-        <v>8.170195327822499</v>
+        <v>8.783989757724999</v>
       </c>
       <c r="T49" s="14" t="n">
-        <v>6.61320634821</v>
+        <v>7.36663300079</v>
       </c>
       <c r="U49" s="14" t="n">
-        <v>8.118383756857501</v>
+        <v>8.5937883897425</v>
       </c>
       <c r="V49" s="14" t="n">
-        <v>5.27080423352</v>
+        <v>8.600459435435001</v>
       </c>
       <c r="W49" s="14" t="n">
-        <v>8.974629506622501</v>
+        <v>12.83434846344</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>21.195677265945</v>
+        <v>30.4253862065475</v>
       </c>
       <c r="Y49" s="14" t="n">
-        <v>12.6398899049675</v>
+        <v>18.51532213713</v>
       </c>
       <c r="Z49" s="14" t="n">
-        <v>0.01361900988</v>
+        <v>0.01878519328</v>
       </c>
       <c r="AA49" s="14" t="n">
         <v>13.13</v>
@@ -4403,43 +4403,43 @@
         <v>2.57</v>
       </c>
       <c r="N50" s="13" t="n">
-        <v>22.26390392121</v>
+        <v>22.94248658667</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>12.1308556937085</v>
+        <v>11.87584704033</v>
       </c>
       <c r="P50" s="13" t="n">
-        <v>31.723021234625</v>
+        <v>31.5692050461375</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>60.23413009803</v>
+        <v>60.0111268667575</v>
       </c>
       <c r="R50" s="13" t="n">
-        <v>7.8150272832415</v>
+        <v>7.377691034945</v>
       </c>
       <c r="S50" s="13" t="n">
-        <v>7.6036973733175</v>
+        <v>8.870086420650001</v>
       </c>
       <c r="T50" s="13" t="n">
-        <v>8.2925359139525</v>
+        <v>9.565057547325001</v>
       </c>
       <c r="U50" s="13" t="n">
-        <v>11.4502311387625</v>
+        <v>11.869277120855</v>
       </c>
       <c r="V50" s="13" t="n">
-        <v>10.58197302456</v>
+        <v>13.34786442052</v>
       </c>
       <c r="W50" s="13" t="n">
-        <v>10.8780843458525</v>
+        <v>15.001203537005</v>
       </c>
       <c r="X50" s="13" t="n">
-        <v>34.4363381277125</v>
+        <v>42.3298128672825</v>
       </c>
       <c r="Y50" s="13" t="n">
-        <v>13.16433254507</v>
+        <v>20.22242560422</v>
       </c>
       <c r="Z50" s="13" t="n">
-        <v>0.0186368868175</v>
+        <v>0.031180561405</v>
       </c>
       <c r="AA50" s="13" t="n">
         <v>16.97</v>
@@ -4498,43 +4498,43 @@
         <v>1.43</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>36.372676245164</v>
+        <v>37.23076510251</v>
       </c>
       <c r="O51" s="14" t="n">
-        <v>21.1198800682625</v>
+        <v>20.58716702875</v>
       </c>
       <c r="P51" s="14" t="n">
-        <v>29.633012205132</v>
+        <v>29.21431513336</v>
       </c>
       <c r="Q51" s="14" t="n">
-        <v>61.2185974638805</v>
+        <v>61.3073982527125</v>
       </c>
       <c r="R51" s="14" t="n">
-        <v>11.8432788046615</v>
+        <v>11.50404242204</v>
       </c>
       <c r="S51" s="14" t="n">
-        <v>13.086777979205</v>
+        <v>14.77958974205</v>
       </c>
       <c r="T51" s="14" t="n">
-        <v>9.642421455275</v>
+        <v>10.57202593776</v>
       </c>
       <c r="U51" s="14" t="n">
-        <v>13.025572768635</v>
+        <v>14.432984803125</v>
       </c>
       <c r="V51" s="14" t="n">
-        <v>10.5703272721025</v>
+        <v>13.608596849715</v>
       </c>
       <c r="W51" s="14" t="n">
-        <v>10.11239461239</v>
+        <v>14.361834820445</v>
       </c>
       <c r="X51" s="14" t="n">
-        <v>29.02213971181</v>
+        <v>38.077968959765</v>
       </c>
       <c r="Y51" s="14" t="n">
-        <v>7.9593122325325</v>
+        <v>16.159692300885</v>
       </c>
       <c r="Z51" s="14" t="n">
-        <v>1.5863454042625</v>
+        <v>5.658317594825</v>
       </c>
       <c r="AA51" s="14" t="n">
         <v>17.59</v>
@@ -4593,43 +4593,43 @@
         <v>0.21</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>47.943933484846</v>
+        <v>48.8170449919775</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>29.68278060706</v>
+        <v>29.5563466263625</v>
       </c>
       <c r="P52" s="13" t="n">
-        <v>24.082883321742</v>
+        <v>23.7360169433975</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>73.4878909764475</v>
+        <v>74.08212661522749</v>
       </c>
       <c r="R52" s="13" t="n">
-        <v>7.223732411301</v>
+        <v>7.348694522015</v>
       </c>
       <c r="S52" s="13" t="n">
-        <v>13.4704284186325</v>
+        <v>15.37215306396</v>
       </c>
       <c r="T52" s="13" t="n">
-        <v>10.76251159648</v>
+        <v>12.162201474465</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>16.48319244971</v>
+        <v>18.435599143185</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>16.79204572332</v>
+        <v>21.34765759448</v>
       </c>
       <c r="W52" s="13" t="n">
-        <v>21.00042376271</v>
+        <v>27.3279444558925</v>
       </c>
       <c r="X52" s="13" t="n">
-        <v>28.5809398573125</v>
+        <v>35.729895043745</v>
       </c>
       <c r="Y52" s="13" t="n">
-        <v>9.9566825347675</v>
+        <v>17.61709932017</v>
       </c>
       <c r="Z52" s="13" t="n">
-        <v>1.2005062200075</v>
+        <v>4.26928513655</v>
       </c>
       <c r="AA52" s="13" t="n">
         <v>22.61</v>
@@ -4688,43 +4688,43 @@
         <v>1.69</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>62.23216715891</v>
+        <v>61.4241064967425</v>
       </c>
       <c r="O53" s="14" t="n">
-        <v>18.6103482358045</v>
+        <v>18.12976512081</v>
       </c>
       <c r="P53" s="14" t="n">
-        <v>36.8635311504075</v>
+        <v>36.68157048969</v>
       </c>
       <c r="Q53" s="14" t="n">
-        <v>87.2543402291505</v>
+        <v>88.094058508225</v>
       </c>
       <c r="R53" s="14" t="n">
-        <v>15.116735957043</v>
+        <v>16.51979919681</v>
       </c>
       <c r="S53" s="14" t="n">
-        <v>16.217760263705</v>
+        <v>18.751289252535</v>
       </c>
       <c r="T53" s="14" t="n">
-        <v>15.9347021896825</v>
+        <v>17.38115583176</v>
       </c>
       <c r="U53" s="14" t="n">
-        <v>8.5584413472075</v>
+        <v>9.421399463945001</v>
       </c>
       <c r="V53" s="14" t="n">
-        <v>17.620462295345</v>
+        <v>21.14153857067</v>
       </c>
       <c r="W53" s="14" t="n">
-        <v>16.395962449545</v>
+        <v>20.68962433146</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>27.2371953593775</v>
+        <v>36.390835307575</v>
       </c>
       <c r="Y53" s="14" t="n">
-        <v>14.6497079658825</v>
+        <v>22.42011739184</v>
       </c>
       <c r="Z53" s="14" t="n">
-        <v>0.860890098495</v>
+        <v>3.09068840178</v>
       </c>
       <c r="AA53" s="14" t="n">
         <v>29.43</v>
